--- a/ADC_LCD/report/ADC Lab Data.xlsx
+++ b/ADC_LCD/report/ADC Lab Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\School\Spring_26\Junior_Design\ADC_LCD\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE9B8FC-539A-43DF-BE52-8C0F75984BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26283E9-21D3-4BBA-8D18-A0B68B2BA565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="2" r:id="rId1"/>
@@ -98,7 +98,212 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -142,10 +347,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Srees Data-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1451,12 +1656,42 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Measured</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Vs. Expected</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.4700693350831146"/>
-          <c:y val="2.9895366218236172E-2"/>
+          <c:x val="0.31529875471988"/>
+          <c:y val="6.5517999436909502E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1555,8 +1790,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.37879658792650917"/>
-                  <c:y val="-0.19302092446777486"/>
+                  <c:x val="-0.44011707021536212"/>
+                  <c:y val="-0.2078960996340613"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -3876,6 +4111,44 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F18CB7D4-6B88-4AA3-9AFF-A66EBF36A9A9}" name="Table1" displayName="Table1" ref="A1:D40" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11">
+  <autoFilter ref="A1:D40" xr:uid="{F18CB7D4-6B88-4AA3-9AFF-A66EBF36A9A9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{BB5AF93D-2E1B-4114-B48D-AE7ACEE5BC6B}" name="Expected Resistance Value (Ohms)" dataDxfId="9">
+      <calculatedColumnFormula>A1+50000</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{096359FE-37E8-4E3E-8520-A88A0A95598E}" name="Measured Resistance Value (Ohms)" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{01DE328F-94F9-4A97-AC3A-C7FB2CB8374E}" name="Difference" dataDxfId="7">
+      <calculatedColumnFormula>A2-B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{EAA50D3F-E11E-47E9-A758-33D260285ADD}" name="Percent Error" dataDxfId="6">
+      <calculatedColumnFormula>ABS((B2-A2)/A2)*100</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F100E413-E237-4DCC-BA72-A3D13D3F12AB}" name="Table2" displayName="Table2" ref="A1:D40" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+  <autoFilter ref="A1:D40" xr:uid="{F100E413-E237-4DCC-BA72-A3D13D3F12AB}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7B26715C-5BCF-4832-BA55-348CCC7E8FC6}" name="Expected Resistance Value (Ohms)" dataDxfId="5">
+      <calculatedColumnFormula>A1+50000</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{B6DEF4BD-BB6F-431A-B796-47D78DC5DA73}" name="Measured Resistance Value (Ohms)" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{03FBE166-8470-451E-8EBA-1CA21ACE6D87}" name="Difference" dataDxfId="0">
+      <calculatedColumnFormula>B2 - A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{51550365-936E-42D2-A7C2-73D560193459}" name="Percent Error" dataDxfId="3">
+      <calculatedColumnFormula>ABS((B2-A2)/A2)*100</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -4078,7 +4351,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="30.5546875" customWidth="1"/>
@@ -4089,7 +4362,7 @@
     <col min="7" max="7" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4104,7 +4377,7 @@
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1000</v>
       </c>
@@ -4121,7 +4394,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>5000</f>
         <v>5000</v>
@@ -4139,7 +4412,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f>A3+5000</f>
         <v>10000</v>
@@ -4157,7 +4430,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A22" si="2">A4+5000</f>
         <v>15000</v>
@@ -4175,7 +4448,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
@@ -4194,7 +4467,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
@@ -4213,7 +4486,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
@@ -4232,7 +4505,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>35000</v>
@@ -4251,7 +4524,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>40000</v>
@@ -4270,7 +4543,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>45000</v>
@@ -4289,7 +4562,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
@@ -4308,7 +4581,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>55000</v>
@@ -4327,7 +4600,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>60000</v>
@@ -4346,7 +4619,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>65000</v>
@@ -4364,7 +4637,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f>A15+5000</f>
         <v>70000</v>
@@ -4382,7 +4655,7 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>75000</v>
@@ -4399,7 +4672,7 @@
         <v>3.135493333333327</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>80000</v>
@@ -4416,7 +4689,7 @@
         <v>3.3680875000000015</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>85000</v>
@@ -4433,7 +4706,7 @@
         <v>1.9078352941176511</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>90000</v>
@@ -4450,7 +4723,7 @@
         <v>0.32059999999999289</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>95000</v>
@@ -4467,7 +4740,7 @@
         <v>1.3323263157894805</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="12.3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>100000</v>
@@ -4484,7 +4757,7 @@
         <v>2.2235599999999978</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f>A22+50000</f>
         <v>150000</v>
@@ -4501,7 +4774,7 @@
         <v>2.2969866666666738</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" ref="A24:A39" si="3">A23+50000</f>
         <v>200000</v>
@@ -4518,7 +4791,7 @@
         <v>3.4870899999999962</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>250000</v>
@@ -4535,7 +4808,7 @@
         <v>1.5228991999999968</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>300000</v>
@@ -4552,7 +4825,7 @@
         <v>6.9984333333333302</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>350000</v>
@@ -4569,7 +4842,7 @@
         <v>6.2581142857142922</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>400000</v>
@@ -4586,7 +4859,7 @@
         <v>3.1169299999999933</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>450000</v>
@@ -4603,7 +4876,7 @@
         <v>10.886600000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>500000</v>
@@ -4620,7 +4893,7 @@
         <v>10.903556000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>550000</v>
@@ -4637,7 +4910,7 @@
         <v>16.796938181818177</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f>A31+50000</f>
         <v>600000</v>
@@ -4654,7 +4927,7 @@
         <v>6.0546833333333296</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>650000</v>
@@ -4671,7 +4944,7 @@
         <v>4.411030769230762</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>700000</v>
@@ -4688,7 +4961,7 @@
         <v>7.4805999999999928</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>750000</v>
@@ -4705,7 +4978,7 @@
         <v>7.8243242666666717</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>800000</v>
@@ -4722,7 +4995,7 @@
         <v>8.4696374999999975</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>850000</v>
@@ -4739,7 +5012,7 @@
         <v>12.824705882352941</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>900000</v>
@@ -4756,7 +5029,7 @@
         <v>19.117366666666673</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>950000</v>
@@ -4773,7 +5046,7 @@
         <v>20.579852631578945</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f>A39+50000</f>
         <v>1000000</v>
@@ -4790,10 +5063,10 @@
         <v>14.770790000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
     </row>
   </sheetData>
@@ -4805,7 +5078,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC702F8D-567E-4CD0-B754-A51187854DB3}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.33203125" customWidth="1"/>
@@ -4813,7 +5086,7 @@
     <col min="4" max="4" width="28.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4827,7 +5100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1000</v>
       </c>
@@ -4843,7 +5116,7 @@
         <v>3.2474999999999907</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>5000</f>
         <v>5000</v>
@@ -4860,7 +5133,7 @@
         <v>0.47219999999999346</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f>A3+5000</f>
         <v>10000</v>
@@ -4877,7 +5150,7 @@
         <v>0.16936999999999899</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A22" si="2">A4+5000</f>
         <v>15000</v>
@@ -4894,7 +5167,7 @@
         <v>0.25599999999999762</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
@@ -4911,7 +5184,7 @@
         <v>8.6839999999992867E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
@@ -4928,7 +5201,7 @@
         <v>0.20667999999999304</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
@@ -4945,7 +5218,7 @@
         <v>1.2028266666666727</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>35000</v>
@@ -4962,7 +5235,7 @@
         <v>0.44342857142856312</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>40000</v>
@@ -4979,7 +5252,7 @@
         <v>1.5264799999999923</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>45000</v>
@@ -4996,7 +5269,7 @@
         <v>1.0237422222222248</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
@@ -5013,7 +5286,7 @@
         <v>1.0528999999999942</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>55000</v>
@@ -5030,7 +5303,7 @@
         <v>1.0222909090909127</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>60000</v>
@@ -5047,7 +5320,7 @@
         <v>1.7382666666666651</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>65000</v>
@@ -5064,7 +5337,7 @@
         <v>0.87083076923075931</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f>A15+5000</f>
         <v>70000</v>
@@ -5081,7 +5354,7 @@
         <v>1.4622171428571373</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>75000</v>
@@ -5098,7 +5371,7 @@
         <v>0.94673333333333731</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>80000</v>
@@ -5115,7 +5388,7 @@
         <v>1.2803750000000036</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>85000</v>
@@ -5132,7 +5405,7 @@
         <v>1.3475858823529459</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>90000</v>
@@ -5149,7 +5422,7 @@
         <v>2.0700555555555589</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>95000</v>
@@ -5166,7 +5439,7 @@
         <v>1.0847684210526303</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>100000</v>
@@ -5183,7 +5456,7 @@
         <v>1.958429999999993</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f>A22+50000</f>
         <v>150000</v>
@@ -5200,7 +5473,7 @@
         <v>1.3014400000000024</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" ref="A24:A39" si="3">A23+50000</f>
         <v>200000</v>
@@ -5217,7 +5490,7 @@
         <v>3.3143080000000049</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>250000</v>
@@ -5234,7 +5507,7 @@
         <v>2.2874560000000055</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>300000</v>
@@ -5251,7 +5524,7 @@
         <v>3.5609266666666759</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>350000</v>
@@ -5268,7 +5541,7 @@
         <v>4.3625428571428637</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>400000</v>
@@ -5285,7 +5558,7 @@
         <v>4.5924879999999977</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>450000</v>
@@ -5302,7 +5575,7 @@
         <v>6.2178577777777742</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>500000</v>
@@ -5319,7 +5592,7 @@
         <v>5.8011840000000081</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>550000</v>
@@ -5336,7 +5609,7 @@
         <v>5.431399999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f>A31+50000</f>
         <v>600000</v>
@@ -5353,7 +5626,7 @@
         <v>10.863260000000009</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>650000</v>
@@ -5370,7 +5643,7 @@
         <v>6.9556769230769273</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>700000</v>
@@ -5387,7 +5660,7 @@
         <v>9.7815314285714248</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>750000</v>
@@ -5404,7 +5677,7 @@
         <v>8.4744799999999962</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>800000</v>
@@ -5421,7 +5694,7 @@
         <v>8.0024499999999978</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>850000</v>
@@ -5438,7 +5711,7 @@
         <v>15.038717647058823</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>900000</v>
@@ -5455,7 +5728,7 @@
         <v>11.220011111111109</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>950000</v>
@@ -5472,7 +5745,7 @@
         <v>10.590863157894733</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f>A39+50000</f>
         <v>1000000</v>
@@ -5498,15 +5771,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D194A0EA-AC92-4F59-8CC8-8AE808E2573F}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="31.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.21875" customWidth="1"/>
     <col min="4" max="4" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5520,7 +5793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1000</v>
       </c>
@@ -5536,7 +5809,7 @@
         <v>7.2404600000000068</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>5000</f>
         <v>5000</v>
@@ -5553,7 +5826,7 @@
         <v>1.6852000000000045</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f>A3+5000</f>
         <v>10000</v>
@@ -5570,7 +5843,7 @@
         <v>1.2557400000000052</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A22" si="2">A4+5000</f>
         <v>15000</v>
@@ -5587,7 +5860,7 @@
         <v>0.87568666666666106</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
@@ -5604,7 +5877,7 @@
         <v>1.1578700000000026</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
@@ -5621,7 +5894,7 @@
         <v>1.2229279999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
@@ -5638,7 +5911,7 @@
         <v>1.4099933333333319</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>35000</v>
@@ -5655,7 +5928,7 @@
         <v>1.6376800000000056</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>40000</v>
@@ -5672,7 +5945,7 @@
         <v>1.4379600000000028</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>45000</v>
@@ -5689,7 +5962,7 @@
         <v>1.3971555555555581</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
@@ -5706,7 +5979,7 @@
         <v>1.4890479999999953</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>55000</v>
@@ -5723,7 +5996,7 @@
         <v>0.44687999999999933</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>60000</v>
@@ -5740,7 +6013,7 @@
         <v>1.8849999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>65000</v>
@@ -5757,7 +6030,7 @@
         <v>1.9180153846153944</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f>A15+5000</f>
         <v>70000</v>
@@ -5774,7 +6047,7 @@
         <v>2.2065285714285814</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>75000</v>
@@ -5791,7 +6064,7 @@
         <v>2.0670933333333426</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>80000</v>
@@ -5808,7 +6081,7 @@
         <v>2.078824999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>85000</v>
@@ -5825,7 +6098,7 @@
         <v>2.3013411764705878</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>90000</v>
@@ -5842,7 +6115,7 @@
         <v>2.5502133333333283</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>95000</v>
@@ -5859,7 +6132,7 @@
         <v>2.1014105263157856</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>100000</v>
@@ -5876,7 +6149,7 @@
         <v>3.2987679999999964</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f>A22+50000</f>
         <v>150000</v>
@@ -5893,7 +6166,7 @@
         <v>4.2906266666666681</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" ref="A24:A39" si="3">A23+50000</f>
         <v>200000</v>
@@ -5910,7 +6183,7 @@
         <v>5.6134100000000036</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>250000</v>
@@ -5927,7 +6200,7 @@
         <v>6.0646159999999911</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>300000</v>
@@ -5944,7 +6217,7 @@
         <v>6.8552866666666619</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>350000</v>
@@ -5961,7 +6234,7 @@
         <v>7.8596685714285783</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>400000</v>
@@ -5978,7 +6251,7 @@
         <v>8.9833325000000048</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>450000</v>
@@ -5995,7 +6268,7 @@
         <v>9.8962000000000057</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>500000</v>
@@ -6012,7 +6285,7 @@
         <v>13.47173999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>550000</v>
@@ -6029,7 +6302,7 @@
         <v>13.22358545454545</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f>A31+50000</f>
         <v>600000</v>
@@ -6046,7 +6319,7 @@
         <v>13.618072666666665</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>650000</v>
@@ -6063,7 +6336,7 @@
         <v>13.674446153846157</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>700000</v>
@@ -6080,7 +6353,7 @@
         <v>14.403285714285714</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>750000</v>
@@ -6097,7 +6370,7 @@
         <v>17.292922666666673</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>800000</v>
@@ -6114,7 +6387,7 @@
         <v>19.121975000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>850000</v>
@@ -6131,7 +6404,7 @@
         <v>21.248357647058828</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>900000</v>
@@ -6148,7 +6421,7 @@
         <v>21.406044444444433</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>950000</v>
@@ -6165,7 +6438,7 @@
         <v>23.479663157894741</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f>A39+50000</f>
         <v>1000000</v>
@@ -6185,21 +6458,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA07D4A-8DF4-43C5-B23B-FADCF3142A94}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6213,7 +6489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1000</v>
       </c>
@@ -6221,15 +6497,15 @@
         <v>1037.8240000000001</v>
       </c>
       <c r="C2" s="1">
-        <f>A2-B2</f>
-        <v>-37.824000000000069</v>
+        <f t="shared" ref="C2:C40" si="0">B2 - A2</f>
+        <v>37.824000000000069</v>
       </c>
       <c r="D2" s="1">
         <f>ABS((B2-A2)/A2)*100</f>
         <v>3.7824000000000066</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>5000</f>
         <v>5000</v>
@@ -6238,15 +6514,15 @@
         <v>4991.4539999999997</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C39" si="0">A3-B3</f>
-        <v>8.5460000000002765</v>
+        <f t="shared" si="0"/>
+        <v>-8.5460000000002765</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D39" si="1">ABS((B3-A3)/A3)*100</f>
+        <f>ABS((B3-A3)/A3)*100</f>
         <v>0.17092000000000551</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f>A3+5000</f>
         <v>10000</v>
@@ -6256,16 +6532,16 @@
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
-        <v>88.836999999999534</v>
+        <v>-88.836999999999534</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B4-A4)/A4)*100</f>
         <v>0.88836999999999522</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A22" si="2">A4+5000</f>
+        <f t="shared" ref="A5:A22" si="1">A4+5000</f>
         <v>15000</v>
       </c>
       <c r="B5" s="1">
@@ -6273,16 +6549,16 @@
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
-        <v>151.99699999999939</v>
+        <v>-151.99699999999939</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B5-A5)/A5)*100</f>
         <v>1.0133133333333293</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20000</v>
       </c>
       <c r="B6" s="1">
@@ -6290,16 +6566,16 @@
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
-        <v>141.06999999999971</v>
+        <v>-141.06999999999971</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B6-A6)/A6)*100</f>
         <v>0.70534999999999848</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
       <c r="B7" s="1">
@@ -6307,16 +6583,16 @@
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>166.82600000000093</v>
+        <v>-166.82600000000093</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B7-A7)/A7)*100</f>
         <v>0.66730400000000367</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="B8" s="1">
@@ -6324,33 +6600,33 @@
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>272.90000000000146</v>
+        <v>-272.90000000000146</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B8-A8)/A8)*100</f>
         <v>0.90966666666667151</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>35000</v>
       </c>
       <c r="B9" s="1">
         <v>34747.964</v>
       </c>
       <c r="C9" s="1">
-        <f>A9-B9</f>
-        <v>252.03600000000006</v>
+        <f t="shared" si="0"/>
+        <v>-252.03600000000006</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B9-A9)/A9)*100</f>
         <v>0.72010285714285727</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="B10" s="1">
@@ -6358,16 +6634,16 @@
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>346.54000000000087</v>
+        <v>-346.54000000000087</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B10-A10)/A10)*100</f>
         <v>0.86635000000000217</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="B11" s="1">
@@ -6375,16 +6651,16 @@
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
-        <v>483.34999999999854</v>
+        <v>-483.34999999999854</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B11-A11)/A11)*100</f>
         <v>1.0741111111111079</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>50000</v>
       </c>
       <c r="B12" s="1">
@@ -6392,62 +6668,65 @@
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
-        <v>2432.8099999999977</v>
+        <v>-2432.8099999999977</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B12-A12)/A12)*100</f>
         <v>4.8656199999999954</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>55000</v>
       </c>
       <c r="B13" s="1">
         <v>54540.296000000002</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1">
+        <f t="shared" si="0"/>
+        <v>-459.7039999999979</v>
+      </c>
       <c r="D13" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B13-A13)/A13)*100</f>
         <v>0.83582545454545065</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60000</v>
       </c>
       <c r="B14" s="1">
         <v>59443.61</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="0"/>
-        <v>556.38999999999942</v>
+        <f>B14 - A14</f>
+        <v>-556.38999999999942</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B14-A14)/A14)*100</f>
         <v>0.92731666666666568</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>65000</v>
       </c>
       <c r="B15" s="1">
         <v>64487.42</v>
       </c>
       <c r="C15" s="1">
-        <f>A15-B15</f>
-        <v>512.58000000000175</v>
+        <f t="shared" si="0"/>
+        <v>-512.58000000000175</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B15-A15)/A15)*100</f>
         <v>0.7885846153846181</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f>A15+5000</f>
         <v>70000</v>
@@ -6456,17 +6735,17 @@
         <v>69472.38</v>
       </c>
       <c r="C16" s="1">
-        <f>A16-B16</f>
-        <v>527.61999999999534</v>
+        <f t="shared" si="0"/>
+        <v>-527.61999999999534</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B16-A16)/A16)*100</f>
         <v>0.7537428571428505</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>75000</v>
       </c>
       <c r="B17" s="1">
@@ -6474,16 +6753,16 @@
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
-        <v>647.30999999999767</v>
+        <v>-647.30999999999767</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B17-A17)/A17)*100</f>
         <v>0.86307999999999696</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80000</v>
       </c>
       <c r="B18" s="1">
@@ -6491,16 +6770,16 @@
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
-        <v>688.74000000000524</v>
+        <v>-688.74000000000524</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B18-A18)/A18)*100</f>
         <v>0.86092500000000649</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>85000</v>
       </c>
       <c r="B19" s="1">
@@ -6508,16 +6787,16 @@
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
-        <v>686.66000000000349</v>
+        <v>-686.66000000000349</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B19-A19)/A19)*100</f>
         <v>0.8078352941176512</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90000</v>
       </c>
       <c r="B20" s="1">
@@ -6525,16 +6804,16 @@
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
-        <v>807.30000000000291</v>
+        <v>-807.30000000000291</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B20-A20)/A20)*100</f>
         <v>0.89700000000000313</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>95000</v>
       </c>
       <c r="B21" s="1">
@@ -6542,16 +6821,16 @@
       </c>
       <c r="C21" s="1">
         <f t="shared" si="0"/>
-        <v>985.69000000000233</v>
+        <v>-985.69000000000233</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B21-A21)/A21)*100</f>
         <v>1.0375684210526341</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100000</v>
       </c>
       <c r="B22" s="1">
@@ -6559,14 +6838,14 @@
       </c>
       <c r="C22" s="1">
         <f t="shared" si="0"/>
-        <v>351.69999999999709</v>
+        <v>-351.69999999999709</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B22-A22)/A22)*100</f>
         <v>0.35169999999999713</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f>A22+50000</f>
         <v>150000</v>
@@ -6576,16 +6855,16 @@
       </c>
       <c r="C23" s="1">
         <f t="shared" si="0"/>
-        <v>1139.3299999999872</v>
+        <v>-1139.3299999999872</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B23-A23)/A23)*100</f>
         <v>0.75955333333332475</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <f t="shared" ref="A24:A39" si="3">A23+50000</f>
+        <f t="shared" ref="A24:A39" si="2">A23+50000</f>
         <v>200000</v>
       </c>
       <c r="B24" s="1">
@@ -6593,16 +6872,16 @@
       </c>
       <c r="C24" s="1">
         <f t="shared" si="0"/>
-        <v>2550.8399999999965</v>
+        <v>-2550.8399999999965</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B24-A24)/A24)*100</f>
         <v>1.2754199999999982</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>250000</v>
       </c>
       <c r="B25" s="1">
@@ -6610,16 +6889,16 @@
       </c>
       <c r="C25" s="1">
         <f t="shared" si="0"/>
-        <v>3139.0320000000065</v>
+        <v>-3139.0320000000065</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B25-A25)/A25)*100</f>
         <v>1.2556128000000026</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>300000</v>
       </c>
       <c r="B26" s="1">
@@ -6627,16 +6906,16 @@
       </c>
       <c r="C26" s="1">
         <f t="shared" si="0"/>
-        <v>2214.4400000000023</v>
+        <v>-2214.4400000000023</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B26-A26)/A26)*100</f>
         <v>0.73814666666666751</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>350000</v>
       </c>
       <c r="B27" s="1">
@@ -6644,16 +6923,16 @@
       </c>
       <c r="C27" s="1">
         <f t="shared" si="0"/>
-        <v>5418.960000000021</v>
+        <v>-5418.960000000021</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B27-A27)/A27)*100</f>
         <v>1.5482742857142917</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400000</v>
       </c>
       <c r="B28" s="1">
@@ -6661,65 +6940,65 @@
       </c>
       <c r="C28" s="1">
         <f t="shared" si="0"/>
-        <v>10503.5</v>
+        <v>-10503.5</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B28-A28)/A28)*100</f>
         <v>2.6258750000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>450000</v>
       </c>
       <c r="B29" s="1">
         <v>438467.96</v>
       </c>
       <c r="C29" s="1">
-        <f>A29-B29</f>
-        <v>11532.039999999979</v>
+        <f t="shared" si="0"/>
+        <v>-11532.039999999979</v>
       </c>
       <c r="D29" s="1">
         <f>ABS((B29-A29)/A29)*100</f>
         <v>2.5626755555555509</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>500000</v>
       </c>
       <c r="B30" s="1">
         <v>483009.02</v>
       </c>
       <c r="C30" s="1">
-        <f>A30-B30</f>
-        <v>16990.979999999981</v>
+        <f t="shared" si="0"/>
+        <v>-16990.979999999981</v>
       </c>
       <c r="D30" s="1">
         <f>ABS((B30-A30)/A30)*100</f>
         <v>3.3981959999999964</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>550000</v>
       </c>
       <c r="B31" s="1">
         <v>533564.30000000005</v>
       </c>
       <c r="C31" s="1">
-        <f>A31-B31</f>
-        <v>16435.699999999953</v>
+        <f t="shared" si="0"/>
+        <v>-16435.699999999953</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B31-A31)/A31)*100</f>
         <v>2.9883090909090826</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f>A31+50000</f>
         <v>600000</v>
@@ -6728,34 +7007,34 @@
         <v>570338.69999999995</v>
       </c>
       <c r="C32" s="1">
-        <f>A32-B32</f>
-        <v>29661.300000000047</v>
+        <f t="shared" si="0"/>
+        <v>-29661.300000000047</v>
       </c>
       <c r="D32" s="1">
         <f>ABS((B32-A32)/A32)*100</f>
         <v>4.9435500000000072</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>650000</v>
       </c>
       <c r="B33" s="1">
         <v>624234.19999999995</v>
       </c>
       <c r="C33" s="1">
-        <f>A33-B33</f>
-        <v>25765.800000000047</v>
+        <f t="shared" si="0"/>
+        <v>-25765.800000000047</v>
       </c>
       <c r="D33" s="1">
         <f>ABS((B33-A33)/A33)*100</f>
         <v>3.9639692307692385</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>700000</v>
       </c>
       <c r="B34" s="1">
@@ -6763,16 +7042,16 @@
       </c>
       <c r="C34" s="1">
         <f t="shared" si="0"/>
-        <v>22837.400000000023</v>
+        <v>-22837.400000000023</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B34-A34)/A34)*100</f>
         <v>3.2624857142857175</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>750000</v>
       </c>
       <c r="B35" s="1">
@@ -6780,50 +7059,50 @@
       </c>
       <c r="C35" s="1">
         <f t="shared" si="0"/>
-        <v>26271.099999999977</v>
+        <v>-26271.099999999977</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B35-A35)/A35)*100</f>
         <v>3.50281333333333</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>800000</v>
       </c>
       <c r="B36" s="1">
         <v>787149.22</v>
       </c>
       <c r="C36" s="1">
-        <f>A36-B36</f>
-        <v>12850.780000000028</v>
+        <f t="shared" si="0"/>
+        <v>-12850.780000000028</v>
       </c>
       <c r="D36" s="1">
         <f>ABS((B36-A36)/A36)*100</f>
         <v>1.6063475000000036</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>850000</v>
       </c>
       <c r="B37" s="1">
         <v>848560.7</v>
       </c>
       <c r="C37" s="1">
-        <f>A37-B37</f>
-        <v>1439.3000000000466</v>
+        <f t="shared" si="0"/>
+        <v>-1439.3000000000466</v>
       </c>
       <c r="D37" s="1">
         <f>ABS((B37-A37)/A37)*100</f>
         <v>0.16932941176471136</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>900000</v>
       </c>
       <c r="B38" s="1">
@@ -6831,16 +7110,16 @@
       </c>
       <c r="C38" s="1">
         <f t="shared" si="0"/>
-        <v>-746.40000000002328</v>
+        <v>746.40000000002328</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B38-A38)/A38)*100</f>
         <v>8.2933333333335926E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>950000</v>
       </c>
       <c r="B39" s="1">
@@ -6848,14 +7127,14 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" si="0"/>
-        <v>-18283.400000000023</v>
+        <v>18283.400000000023</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="1"/>
+        <f>ABS((B39-A39)/A39)*100</f>
         <v>1.9245684210526341</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f>A39+50000</f>
         <v>1000000</v>
@@ -6864,21 +7143,24 @@
         <v>1031624.3</v>
       </c>
       <c r="C40" s="1">
-        <f>A40-B40</f>
-        <v>-31624.300000000047</v>
+        <f t="shared" si="0"/>
+        <v>31624.300000000047</v>
       </c>
       <c r="D40" s="1">
         <f>ABS((B40-A40)/A40)*100</f>
         <v>3.162430000000005</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>